--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260622.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260622.xlsx
@@ -611,56 +611,56 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>13,300,000</t>
+          <t>12,900,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>18.29%</t>
+          <t>18.14%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>10,050,000</t>
+          <t>72,400,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.19%</t>
+          <t>6.49%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>72,400,000</t>
+          <t>10,050,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.01%</t>
+          <t>5.99%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>5.04%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.84%</t>
+          <t>4.82%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.45%</t>
+          <t>4.41%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.31%</t>
+          <t>4.40%</t>
         </is>
       </c>
     </row>
@@ -770,95 +770,95 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>3.67%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>1,320,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.30%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>1,280,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.24%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2,430,000</t>
+          <t>2,100,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2,100,000</t>
+          <t>2,430,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.93%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
@@ -902,73 +902,73 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.15%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>830,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,700,000</t>
+          <t>830,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,240,000</t>
+          <t>4,500,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -990,29 +990,29 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>4,500,000</t>
+          <t>1,240,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1144,29 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>820,000</t>
+          <t>5,600,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1183,56 +1183,56 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>801,000</t>
+          <t>670,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>5,600,000</t>
+          <t>1,950,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>610,000</t>
+          <t>1,572,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1254,183 +1254,183 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,710,000</t>
+          <t>7,550,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>570,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>7,550,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,380,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>570,000</t>
+          <t>1,080,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,080,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>360,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1496,29 +1496,29 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
@@ -1547,144 +1547,144 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>957,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>750,000</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>280,000</t>
+          <t>1,010,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>600,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,010,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>11,350,146,648</t>
+          <t>7,526,415,571</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>3,025,898,691</t>
+          <t>4,922,678,238</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
